--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -1,124 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AiState" sheetId="1" r:id="rId1"/>
+    <sheet name="AiState" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>AiState</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>9a73a0d8abdbff22</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>stable_key</t>
-  </si>
-  <si>
-    <t>graph_id</t>
-  </si>
-  <si>
-    <t>entry_program_id</t>
-  </si>
-  <si>
-    <t>mandatory_fallback_ability_id</t>
-  </si>
-  <si>
-    <t>turn_counter_reset</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>ref&lt;AiGraph.id&gt;</t>
-  </si>
-  <si>
-    <t>optional&lt;ref&lt;Program.id&gt;&gt;</t>
-  </si>
-  <si>
-    <t>ref&lt;EnemyAbility.id&gt;</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>key;range=1..2147483647</t>
-  </si>
-  <si>
-    <t>length=1..160</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -137,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -431,148 +407,559 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AiState</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>9a73a0d8abdbff22</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>graph_id</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>entry_program_id</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>mandatory_fallback_ability_id</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>turn_counter_reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>graph_id</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>entry_program_id</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>mandatory_fallback_ability_id</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>turn_counter_reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ref&lt;AiGraph.id&gt;</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>optional&lt;ref&lt;Program.id&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ref&lt;EnemyAbility.id&gt;</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>length=1..160</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.abundance-sprite-golden-hound.minionlv2.variant.01</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11001</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.frostspawn.minion.variant.01</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13010</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11032</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.harmonious-choir-the-great-septimus.bigboss.variant.01</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13011</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11038</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.incineration-shadewalker.minionlv2.variant.01</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13012</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11047</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.mara-struck-soldier.minionlv2.variant.01</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13013</v>
+      </c>
+      <c r="F12" t="n">
+        <v>11048</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.mara-struck-warden.minionlv2.variant.01</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13014</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11052</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.sableclaw-wolftrooper.minionlv2.variant.01</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13015</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11055</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.voidranger-reaver.minionlv2.variant.01</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13016</v>
+      </c>
+      <c r="F15" t="n">
+        <v>11057</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>17</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.voidranger-trampler.elite.variant.01</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13017</v>
+      </c>
+      <c r="F16" t="n">
+        <v>11062</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.aurumaton-gatekeeper.elite.variant.01</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13002</v>
+      </c>
+      <c r="F17" t="n">
+        <v>11003</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.automaton-spider.minionlv2.variant.01</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13003</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11008</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.cocolia-mother-of-deception.bigboss.variant.01</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13004</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11012</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.disciples-of-sanctus-medicus-ballistarius.minionlv2.variant.01</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13005</v>
+      </c>
+      <c r="F20" t="n">
+        <v>11021</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.disciples-of-sanctus-medicus-shape-shifter.elite.variant.01</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13006</v>
+      </c>
+      <c r="F21" t="n">
+        <v>11025</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.eclipse-wolftrooper.minionlv2.variant.01</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13007</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11027</v>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.entranced-ingenium-illumination-dragonfish.minionlv2.variant.01</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13008</v>
+      </c>
+      <c r="F23" t="n">
+        <v>11030</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>28</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>standard-v1.ai.state.enemy.flamespawn.minion.variant.01</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13009</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11031</v>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -962,6 +962,291 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>980701</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>980010</v>
+      </c>
+      <c r="F25" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>980702</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>980010</v>
+      </c>
+      <c r="F26" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>980703</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>980010</v>
+      </c>
+      <c r="F27" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>980704</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-1.state-4</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>980010</v>
+      </c>
+      <c r="F28" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>980705</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-1.state-5</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>980010</v>
+      </c>
+      <c r="F29" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>980706</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>980011</v>
+      </c>
+      <c r="F30" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>980707</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>980011</v>
+      </c>
+      <c r="F31" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>980708</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>980011</v>
+      </c>
+      <c r="F32" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>980709</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-2.state-4</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>980011</v>
+      </c>
+      <c r="F33" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>980710</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-2.state-5</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>980011</v>
+      </c>
+      <c r="F34" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>980711</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-3.state-1</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>980012</v>
+      </c>
+      <c r="F35" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>980712</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-3.state-2</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>980012</v>
+      </c>
+      <c r="F36" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>980713</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-3.state-3</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>980012</v>
+      </c>
+      <c r="F37" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>980714</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-3.state-4</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>980012</v>
+      </c>
+      <c r="F38" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>980715</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-3.state-5</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>980012</v>
+      </c>
+      <c r="F39" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1247,6 +1247,177 @@
         <v>0</v>
       </c>
     </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>990701</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>990010</v>
+      </c>
+      <c r="F40" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>990702</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>990010</v>
+      </c>
+      <c r="F41" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>990703</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>990010</v>
+      </c>
+      <c r="F42" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>990704</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>990011</v>
+      </c>
+      <c r="F43" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>990705</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>990011</v>
+      </c>
+      <c r="F44" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>990706</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>990011</v>
+      </c>
+      <c r="F45" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>990707</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-3.state-1</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>990012</v>
+      </c>
+      <c r="F46" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>990708</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-3.state-2</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>990012</v>
+      </c>
+      <c r="F47" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>990709</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-3.state-3</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>990012</v>
+      </c>
+      <c r="F48" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1418,6 +1418,196 @@
         <v>0</v>
       </c>
     </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1000701</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1000702</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1000703</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1000704</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-1.state-4</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1000705</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-1.state-5</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1000706</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1000707</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1000708</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1000709</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-2.state-4</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1000710</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-2.state-5</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1608,6 +1608,120 @@
         <v>0</v>
       </c>
     </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1010701</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.ai.initial-bellow</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="G59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1010702</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.ai.initial-absorption</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1010703</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.ai.rain-one</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1010704</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.ai.molten</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1010705</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.ai.rain-two</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1010706</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.ai.reset-absorption</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1722,6 +1722,310 @@
         <v>0</v>
       </c>
     </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1020701</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1020010</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1020702</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1020010</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1020703</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1020010</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1020704</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-1.state-4</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1020010</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1020705</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1020706</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1020707</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1020708</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-2.state-4</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1020709</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-2.state-5</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1020710</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-2.state-6</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1020711</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-3.state-1</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1020712</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-3.state-2</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1020713</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-3.state-3</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1020714</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-3.state-4</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1020715</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-3.state-5</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1020716</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-3.state-6</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G80" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2026,6 +2026,291 @@
         <v>0</v>
       </c>
     </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1030701</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1030010</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1030702</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1030010</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1030703</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1030010</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1030704</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1030705</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1030706</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1030707</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-2.state-4</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1030708</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-2.state-5</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1030709</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-2.state-6</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1030710</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-3.state-1</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1030711</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-3.state-2</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1030712</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-3.state-3</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1030713</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-3.state-4</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1030714</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-3.state-5</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1030715</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-3.state-6</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G95" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,6 +2311,462 @@
         <v>0</v>
       </c>
     </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1040701</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1040010</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1040702</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1040010</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1040703</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1040010</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1040704</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-1.state-4</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1040010</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1040705</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1040706</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1040707</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1040708</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-4</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1040709</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-5</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1040710</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-6</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1040711</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-7</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1040712</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-8</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G107" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1040713</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-9</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1040714</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-10</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G109" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1040715</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-1</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1040716</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-2</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1040717</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-3</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1040718</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-4</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1040719</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-5</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1040720</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-6</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1040721</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-7</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1040722</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-8</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1040723</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-9</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1040724</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-10</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G119" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2767,6 +2767,101 @@
         <v>0</v>
       </c>
     </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1050701</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.ai.initial-lament</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1050101</v>
+      </c>
+      <c r="G120" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1050702</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.ai.initial-absorption</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1050101</v>
+      </c>
+      <c r="G121" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1050703</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.ai.rain</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1050101</v>
+      </c>
+      <c r="G122" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1050704</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.ai.enhanced-lament</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1050101</v>
+      </c>
+      <c r="G123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1050705</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.ai.reset-absorption</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1050101</v>
+      </c>
+      <c r="G124" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2862,6 +2862,253 @@
         <v>0</v>
       </c>
     </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1060701</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1060010</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1060702</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1060010</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G126" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1060703</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1060010</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1060704</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-1.state-4</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1060010</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>1060721</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1060011</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G129" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>1060722</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1060011</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>1060723</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1060011</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>1060724</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-2.state-4</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1060011</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1060741</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-3.state-1</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1060012</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1060742</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-3.state-2</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1060012</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>1060743</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-3.state-3</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1060012</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G135" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1060744</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-3.state-4</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1060012</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G136" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>1060745</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-3.state-5</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1060012</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G137" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:J149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3109,6 +3109,234 @@
         <v>0</v>
       </c>
     </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>1070701</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-1.step-1-midnight</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1070010</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G138" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>1070702</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-1.step-2-caressing</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1070010</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>1070703</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-1.step-3-mockery</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1070010</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G140" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>1070704</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-1.step-4-spirit</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1070010</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G141" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>1070705</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-2.step-1-midnight</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1070011</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G142" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>1070706</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-2.step-2-caressing</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1070011</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G143" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>1070707</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-2.step-3-mockery</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1070011</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G144" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>1070708</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-2.step-4-psychological</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1070011</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G145" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1070709</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-3.step-1-caressing</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1070012</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G146" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>1070710</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-3.step-2-mockery</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1070012</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G147" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1070711</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-3.step-3-seething</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1070012</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>1070712</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-3.step-4-psychological</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1070012</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G149" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3337,6 +3337,253 @@
         <v>0</v>
       </c>
     </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>1080701</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-1.step-1-emergency</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1080010</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G150" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>1080702</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-1.step-2-banishing</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1080010</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G151" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>1080703</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-1.step-3-burning</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1080010</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G152" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>1080704</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-1.step-4-power</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1080010</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>1080705</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-2.step-1-tactical</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1080011</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G154" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1080706</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-2.step-2-bombardment</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1080011</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G155" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>1080707</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-2.step-3-banishing</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1080011</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G156" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>1080708</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-2.step-4-burning</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1080011</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G157" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>1080709</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-2.step-5-power</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1080011</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>1080710</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-3.step-1-boost</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1080012</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G159" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>1080711</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-3.step-2-bombardment</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1080012</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G160" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>1080712</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-3.step-3-banishing</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1080012</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G161" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>1080713</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-3.step-4-burning</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1080012</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G162" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J162"/>
+  <dimension ref="A1:J199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3584,6 +3584,709 @@
         <v>0</v>
       </c>
     </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1094101</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1090041</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1090102</v>
+      </c>
+      <c r="G163" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>1094102</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1090042</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1090122</v>
+      </c>
+      <c r="G164" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1094103</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.2.step-2</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1090042</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1090122</v>
+      </c>
+      <c r="G165" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>1094104</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.2.step-3</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1090042</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1090122</v>
+      </c>
+      <c r="G166" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>1094105</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.2.step-4</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1090042</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1090122</v>
+      </c>
+      <c r="G167" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>1094106</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1090043</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1090142</v>
+      </c>
+      <c r="G168" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>1094107</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.3.step-2</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1090043</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1090142</v>
+      </c>
+      <c r="G169" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>1094108</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.3.step-3</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1090043</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1090142</v>
+      </c>
+      <c r="G170" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>1094109</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.3.step-4</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1090043</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1090142</v>
+      </c>
+      <c r="G171" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>1094110</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.4.step-1</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1090044</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1090162</v>
+      </c>
+      <c r="G172" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1094111</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.4.step-2</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1090044</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1090162</v>
+      </c>
+      <c r="G173" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>1094112</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.5.step-1</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1090045</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1090182</v>
+      </c>
+      <c r="G174" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>1094113</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.6.step-1</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1090046</v>
+      </c>
+      <c r="F175" t="n">
+        <v>1090202</v>
+      </c>
+      <c r="G175" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>1094114</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.6.step-2</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1090046</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1090202</v>
+      </c>
+      <c r="G176" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>1094115</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.6.step-3</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1090046</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1090202</v>
+      </c>
+      <c r="G177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>1094116</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.7.step-1</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1090222</v>
+      </c>
+      <c r="G178" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>1094117</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.7.step-2</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1090222</v>
+      </c>
+      <c r="G179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>1094118</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.7.step-3</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1090222</v>
+      </c>
+      <c r="G180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>1094119</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.7.step-4</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1090222</v>
+      </c>
+      <c r="G181" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>1094120</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.7.step-5</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1090222</v>
+      </c>
+      <c r="G182" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1094121</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.7.step-6</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1090222</v>
+      </c>
+      <c r="G183" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>1094122</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.8.step-1</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1090242</v>
+      </c>
+      <c r="G184" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1094123</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.8.step-2</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1090242</v>
+      </c>
+      <c r="G185" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>1094124</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.8.step-3</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="F186" t="n">
+        <v>1090242</v>
+      </c>
+      <c r="G186" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1094125</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.8.step-4</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1090242</v>
+      </c>
+      <c r="G187" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>1094126</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.9.step-1</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1090049</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1090262</v>
+      </c>
+      <c r="G188" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>1094127</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.10.step-1</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1090050</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1090282</v>
+      </c>
+      <c r="G189" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>1094128</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.10.step-2</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1090050</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1090282</v>
+      </c>
+      <c r="G190" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1094129</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.10.step-3</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1090050</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1090282</v>
+      </c>
+      <c r="G191" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>1094130</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.10.step-4</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1090050</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1090282</v>
+      </c>
+      <c r="G192" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>1094131</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.11.step-1</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1090302</v>
+      </c>
+      <c r="G193" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>1094132</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.11.step-2</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1090302</v>
+      </c>
+      <c r="G194" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1094133</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.11.step-3</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1090302</v>
+      </c>
+      <c r="G195" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>1094134</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.11.step-4</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1090302</v>
+      </c>
+      <c r="G196" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>1094135</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.11.step-5</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="F197" t="n">
+        <v>1090302</v>
+      </c>
+      <c r="G197" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1094136</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.12.step-1</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1090052</v>
+      </c>
+      <c r="F198" t="n">
+        <v>1090322</v>
+      </c>
+      <c r="G198" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>1094137</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.12.step-2</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1090052</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1090322</v>
+      </c>
+      <c r="G199" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J199"/>
+  <dimension ref="A1:J233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4287,6 +4287,652 @@
         <v>0</v>
       </c>
     </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>1104101</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1100041</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1100102</v>
+      </c>
+      <c r="G200" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>1104102</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.1.step-2</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1100041</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1100102</v>
+      </c>
+      <c r="G201" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1104103</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.1.step-3</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1100041</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1100102</v>
+      </c>
+      <c r="G202" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>1104104</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1100042</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1100122</v>
+      </c>
+      <c r="G203" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>1104105</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>1100043</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1100142</v>
+      </c>
+      <c r="G204" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1104106</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.3.step-2</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>1100043</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1100142</v>
+      </c>
+      <c r="G205" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1104107</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.4.step-1</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1100044</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1100162</v>
+      </c>
+      <c r="G206" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>1104108</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.4.step-2</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>1100044</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1100162</v>
+      </c>
+      <c r="G207" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>1104109</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.4.step-3</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1100044</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1100162</v>
+      </c>
+      <c r="G208" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>1104110</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.4.step-4</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>1100044</v>
+      </c>
+      <c r="F209" t="n">
+        <v>1100162</v>
+      </c>
+      <c r="G209" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>1104111</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.5.step-1</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1100045</v>
+      </c>
+      <c r="F210" t="n">
+        <v>1100182</v>
+      </c>
+      <c r="G210" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>1104112</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.6.step-1</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1100046</v>
+      </c>
+      <c r="F211" t="n">
+        <v>1100202</v>
+      </c>
+      <c r="G211" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>1104113</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.6.step-2</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1100046</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1100202</v>
+      </c>
+      <c r="G212" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>1104114</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.7.step-1</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1100047</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1100224</v>
+      </c>
+      <c r="G213" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>1104115</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.7.step-2</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1100047</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1100224</v>
+      </c>
+      <c r="G214" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>1104116</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.7.step-3</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1100047</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1100224</v>
+      </c>
+      <c r="G215" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>1104117</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.7.step-4</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1100047</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1100224</v>
+      </c>
+      <c r="G216" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>1104118</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.8.step-1</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1100048</v>
+      </c>
+      <c r="F217" t="n">
+        <v>1100244</v>
+      </c>
+      <c r="G217" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>1104119</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.8.step-2</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1100048</v>
+      </c>
+      <c r="F218" t="n">
+        <v>1100244</v>
+      </c>
+      <c r="G218" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>1104120</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.8.step-3</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1100048</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1100244</v>
+      </c>
+      <c r="G219" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>1104121</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.8.step-4</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1100048</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1100244</v>
+      </c>
+      <c r="G220" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>1104122</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.9.step-1</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1100262</v>
+      </c>
+      <c r="G221" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>1104123</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.9.step-2</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1100262</v>
+      </c>
+      <c r="G222" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>1104124</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.9.step-3</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="F223" t="n">
+        <v>1100262</v>
+      </c>
+      <c r="G223" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>1104125</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.9.step-4</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="F224" t="n">
+        <v>1100262</v>
+      </c>
+      <c r="G224" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>1104126</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.9.step-5</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="F225" t="n">
+        <v>1100262</v>
+      </c>
+      <c r="G225" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>1104127</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.10.step-1</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="F226" t="n">
+        <v>1100282</v>
+      </c>
+      <c r="G226" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>1104128</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.10.step-2</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1100282</v>
+      </c>
+      <c r="G227" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>1104129</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.10.step-3</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="F228" t="n">
+        <v>1100282</v>
+      </c>
+      <c r="G228" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>1104130</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.10.step-4</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="F229" t="n">
+        <v>1100282</v>
+      </c>
+      <c r="G229" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>1104131</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.10.step-5</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1100282</v>
+      </c>
+      <c r="G230" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>1104132</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.11.step-1</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>1100051</v>
+      </c>
+      <c r="F231" t="n">
+        <v>1100302</v>
+      </c>
+      <c r="G231" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>1104133</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.12.step-1</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>1100052</v>
+      </c>
+      <c r="F232" t="n">
+        <v>1100322</v>
+      </c>
+      <c r="G232" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>1104134</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.12.step-2</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1100052</v>
+      </c>
+      <c r="F233" t="n">
+        <v>1100322</v>
+      </c>
+      <c r="G233" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J233"/>
+  <dimension ref="A1:J259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4933,6 +4933,500 @@
         <v>0</v>
       </c>
     </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>1114101</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>1110041</v>
+      </c>
+      <c r="F234" t="n">
+        <v>1110102</v>
+      </c>
+      <c r="G234" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>1114102</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.1.step-2</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>1110041</v>
+      </c>
+      <c r="F235" t="n">
+        <v>1110102</v>
+      </c>
+      <c r="G235" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>1114103</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.1.step-3</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>1110041</v>
+      </c>
+      <c r="F236" t="n">
+        <v>1110102</v>
+      </c>
+      <c r="G236" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>1114104</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>1110042</v>
+      </c>
+      <c r="F237" t="n">
+        <v>1110122</v>
+      </c>
+      <c r="G237" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>1114105</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>1110043</v>
+      </c>
+      <c r="F238" t="n">
+        <v>1110142</v>
+      </c>
+      <c r="G238" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>1114106</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.3.step-2</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>1110043</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1110142</v>
+      </c>
+      <c r="G239" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>1114107</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.3.step-3</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1110043</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1110142</v>
+      </c>
+      <c r="G240" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>1114108</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.3.step-4</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>1110043</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1110142</v>
+      </c>
+      <c r="G241" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>1114109</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.4.step-1</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>1110044</v>
+      </c>
+      <c r="F242" t="n">
+        <v>1110162</v>
+      </c>
+      <c r="G242" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>1114110</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.4.step-2</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>1110044</v>
+      </c>
+      <c r="F243" t="n">
+        <v>1110162</v>
+      </c>
+      <c r="G243" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>1114111</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.4.step-3</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1110044</v>
+      </c>
+      <c r="F244" t="n">
+        <v>1110162</v>
+      </c>
+      <c r="G244" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>1114112</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.4.step-4</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1110044</v>
+      </c>
+      <c r="F245" t="n">
+        <v>1110162</v>
+      </c>
+      <c r="G245" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>1114113</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.5.step-1</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>1110045</v>
+      </c>
+      <c r="F246" t="n">
+        <v>1110182</v>
+      </c>
+      <c r="G246" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>1114114</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.5.step-2</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>1110045</v>
+      </c>
+      <c r="F247" t="n">
+        <v>1110182</v>
+      </c>
+      <c r="G247" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>1114115</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.5.step-3</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>1110045</v>
+      </c>
+      <c r="F248" t="n">
+        <v>1110182</v>
+      </c>
+      <c r="G248" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>1114116</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.6.step-1</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>1110046</v>
+      </c>
+      <c r="F249" t="n">
+        <v>1110202</v>
+      </c>
+      <c r="G249" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>1114117</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.7.step-1</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>1110047</v>
+      </c>
+      <c r="F250" t="n">
+        <v>1110222</v>
+      </c>
+      <c r="G250" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>1114118</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.8.step-1</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>1110048</v>
+      </c>
+      <c r="F251" t="n">
+        <v>1110242</v>
+      </c>
+      <c r="G251" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>1114119</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.9.step-1</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>1110049</v>
+      </c>
+      <c r="F252" t="n">
+        <v>1110262</v>
+      </c>
+      <c r="G252" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>1114120</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.10.step-1</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>1110050</v>
+      </c>
+      <c r="F253" t="n">
+        <v>1110282</v>
+      </c>
+      <c r="G253" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>1114121</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.11.step-1</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="F254" t="n">
+        <v>1110303</v>
+      </c>
+      <c r="G254" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>1114122</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.11.step-2</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="F255" t="n">
+        <v>1110303</v>
+      </c>
+      <c r="G255" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>1114123</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.11.step-3</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="F256" t="n">
+        <v>1110303</v>
+      </c>
+      <c r="G256" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>1114124</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.11.step-4</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="F257" t="n">
+        <v>1110303</v>
+      </c>
+      <c r="G257" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>1114125</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.11.step-5</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="F258" t="n">
+        <v>1110303</v>
+      </c>
+      <c r="G258" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>1114126</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.12.step-1</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>1110052</v>
+      </c>
+      <c r="F259" t="n">
+        <v>1110322</v>
+      </c>
+      <c r="G259" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J259"/>
+  <dimension ref="A1:J282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5427,6 +5427,443 @@
         <v>1</v>
       </c>
     </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>1124101</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>1120041</v>
+      </c>
+      <c r="F260" t="n">
+        <v>1120102</v>
+      </c>
+      <c r="G260" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>1124102</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>1120042</v>
+      </c>
+      <c r="F261" t="n">
+        <v>1120122</v>
+      </c>
+      <c r="G261" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>1124103</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F262" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G262" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>1124104</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-2</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F263" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G263" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>1124105</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-3</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F264" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G264" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>1124106</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-4</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F265" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G265" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>1124107</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-5</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F266" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G266" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>1124108</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-6</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F267" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G267" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>1124109</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-7</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F268" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G268" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>1124110</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.4.step-1</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>1120044</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1120164</v>
+      </c>
+      <c r="G269" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>1124111</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.4.step-2</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>1120044</v>
+      </c>
+      <c r="F270" t="n">
+        <v>1120164</v>
+      </c>
+      <c r="G270" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>1124112</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.4.step-3</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>1120044</v>
+      </c>
+      <c r="F271" t="n">
+        <v>1120164</v>
+      </c>
+      <c r="G271" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>1124113</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.5.step-1</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>1120045</v>
+      </c>
+      <c r="F272" t="n">
+        <v>1120182</v>
+      </c>
+      <c r="G272" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>1124114</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.6.step-1</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>1120046</v>
+      </c>
+      <c r="F273" t="n">
+        <v>1120202</v>
+      </c>
+      <c r="G273" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>1124115</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.6.step-2</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>1120046</v>
+      </c>
+      <c r="F274" t="n">
+        <v>1120202</v>
+      </c>
+      <c r="G274" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>1124116</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.7.step-1</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>1120047</v>
+      </c>
+      <c r="F275" t="n">
+        <v>1120222</v>
+      </c>
+      <c r="G275" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>1124117</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.7.step-2</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>1120047</v>
+      </c>
+      <c r="F276" t="n">
+        <v>1120222</v>
+      </c>
+      <c r="G276" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>1124118</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.8.step-1</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>1120048</v>
+      </c>
+      <c r="F277" t="n">
+        <v>1120242</v>
+      </c>
+      <c r="G277" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>1124119</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.9.step-1</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>1120049</v>
+      </c>
+      <c r="F278" t="n">
+        <v>1120263</v>
+      </c>
+      <c r="G278" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>1124120</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.10.step-1</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>1120050</v>
+      </c>
+      <c r="F279" t="n">
+        <v>1120283</v>
+      </c>
+      <c r="G279" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>1124121</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.10.step-2</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>1120050</v>
+      </c>
+      <c r="F280" t="n">
+        <v>1120283</v>
+      </c>
+      <c r="G280" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>1124122</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.11.step-1</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>1120051</v>
+      </c>
+      <c r="F281" t="n">
+        <v>1120302</v>
+      </c>
+      <c r="G281" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>1124123</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.12.step-1</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>1120052</v>
+      </c>
+      <c r="F282" t="n">
+        <v>1120322</v>
+      </c>
+      <c r="G282" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J282"/>
+  <dimension ref="A1:J319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5864,6 +5864,709 @@
         <v>1</v>
       </c>
     </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>1134101</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>1130041</v>
+      </c>
+      <c r="F283" t="n">
+        <v>1130102</v>
+      </c>
+      <c r="G283" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>1134102</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.1.step-2</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>1130041</v>
+      </c>
+      <c r="F284" t="n">
+        <v>1130102</v>
+      </c>
+      <c r="G284" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>1134103</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.1.step-3</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>1130041</v>
+      </c>
+      <c r="F285" t="n">
+        <v>1130102</v>
+      </c>
+      <c r="G285" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>1134104</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.1.step-4</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>1130041</v>
+      </c>
+      <c r="F286" t="n">
+        <v>1130102</v>
+      </c>
+      <c r="G286" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>1134105</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>1130042</v>
+      </c>
+      <c r="F287" t="n">
+        <v>1130122</v>
+      </c>
+      <c r="G287" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>1134106</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>1130043</v>
+      </c>
+      <c r="F288" t="n">
+        <v>1130145</v>
+      </c>
+      <c r="G288" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>1134107</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.3.step-2</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>1130043</v>
+      </c>
+      <c r="F289" t="n">
+        <v>1130145</v>
+      </c>
+      <c r="G289" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>1134108</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.3.step-3</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>1130043</v>
+      </c>
+      <c r="F290" t="n">
+        <v>1130145</v>
+      </c>
+      <c r="G290" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>1134109</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.3.step-4</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>1130043</v>
+      </c>
+      <c r="F291" t="n">
+        <v>1130145</v>
+      </c>
+      <c r="G291" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>1134110</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.4.step-1</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>1130044</v>
+      </c>
+      <c r="F292" t="n">
+        <v>1130167</v>
+      </c>
+      <c r="G292" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>1134111</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.4.step-2</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>1130044</v>
+      </c>
+      <c r="F293" t="n">
+        <v>1130167</v>
+      </c>
+      <c r="G293" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>1134112</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.4.step-3</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>1130044</v>
+      </c>
+      <c r="F294" t="n">
+        <v>1130167</v>
+      </c>
+      <c r="G294" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>1134113</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.4.step-4</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>1130044</v>
+      </c>
+      <c r="F295" t="n">
+        <v>1130167</v>
+      </c>
+      <c r="G295" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>1134114</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.5.step-1</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>1130045</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1130187</v>
+      </c>
+      <c r="G296" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>1134115</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.5.step-2</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>1130045</v>
+      </c>
+      <c r="F297" t="n">
+        <v>1130187</v>
+      </c>
+      <c r="G297" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>1134116</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.5.step-3</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>1130045</v>
+      </c>
+      <c r="F298" t="n">
+        <v>1130187</v>
+      </c>
+      <c r="G298" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>1134117</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.5.step-4</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>1130045</v>
+      </c>
+      <c r="F299" t="n">
+        <v>1130187</v>
+      </c>
+      <c r="G299" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>1134118</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.6.step-1</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>1130046</v>
+      </c>
+      <c r="F300" t="n">
+        <v>1130203</v>
+      </c>
+      <c r="G300" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>1134119</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.6.step-2</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>1130046</v>
+      </c>
+      <c r="F301" t="n">
+        <v>1130203</v>
+      </c>
+      <c r="G301" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>1134120</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.7.step-1</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>1130047</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1130222</v>
+      </c>
+      <c r="G302" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>1134121</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.8.step-1</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>1130048</v>
+      </c>
+      <c r="F303" t="n">
+        <v>1130245</v>
+      </c>
+      <c r="G303" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>1134122</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.8.step-2</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>1130048</v>
+      </c>
+      <c r="F304" t="n">
+        <v>1130245</v>
+      </c>
+      <c r="G304" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>1134123</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.8.step-3</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>1130048</v>
+      </c>
+      <c r="F305" t="n">
+        <v>1130245</v>
+      </c>
+      <c r="G305" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>1134124</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.8.step-4</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>1130048</v>
+      </c>
+      <c r="F306" t="n">
+        <v>1130245</v>
+      </c>
+      <c r="G306" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>1134125</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.9.step-1</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>1130049</v>
+      </c>
+      <c r="F307" t="n">
+        <v>1130262</v>
+      </c>
+      <c r="G307" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>1134126</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.10.step-1</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>1130050</v>
+      </c>
+      <c r="F308" t="n">
+        <v>1130284</v>
+      </c>
+      <c r="G308" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>1134127</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.10.step-2</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>1130050</v>
+      </c>
+      <c r="F309" t="n">
+        <v>1130284</v>
+      </c>
+      <c r="G309" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>1134128</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.10.step-3</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>1130050</v>
+      </c>
+      <c r="F310" t="n">
+        <v>1130284</v>
+      </c>
+      <c r="G310" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>1134129</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.10.step-4</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>1130050</v>
+      </c>
+      <c r="F311" t="n">
+        <v>1130284</v>
+      </c>
+      <c r="G311" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>1134130</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.11.step-1</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>1130051</v>
+      </c>
+      <c r="F312" t="n">
+        <v>1130304</v>
+      </c>
+      <c r="G312" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>1134131</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.11.step-2</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>1130051</v>
+      </c>
+      <c r="F313" t="n">
+        <v>1130304</v>
+      </c>
+      <c r="G313" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>1134132</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.11.step-3</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>1130051</v>
+      </c>
+      <c r="F314" t="n">
+        <v>1130304</v>
+      </c>
+      <c r="G314" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>1134133</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.11.step-4</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>1130051</v>
+      </c>
+      <c r="F315" t="n">
+        <v>1130304</v>
+      </c>
+      <c r="G315" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>1134134</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.12.step-1</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>1130052</v>
+      </c>
+      <c r="F316" t="n">
+        <v>1130325</v>
+      </c>
+      <c r="G316" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="n">
+        <v>1134135</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.12.step-2</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>1130052</v>
+      </c>
+      <c r="F317" t="n">
+        <v>1130325</v>
+      </c>
+      <c r="G317" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="n">
+        <v>1134136</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.12.step-3</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>1130052</v>
+      </c>
+      <c r="F318" t="n">
+        <v>1130325</v>
+      </c>
+      <c r="G318" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="n">
+        <v>1134137</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.12.step-4</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>1130052</v>
+      </c>
+      <c r="F319" t="n">
+        <v>1130325</v>
+      </c>
+      <c r="G319" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J319"/>
+  <dimension ref="A1:J351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6567,6 +6567,614 @@
         <v>0</v>
       </c>
     </row>
+    <row r="320">
+      <c r="B320" t="n">
+        <v>1144101</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>1140041</v>
+      </c>
+      <c r="F320" t="n">
+        <v>1140102</v>
+      </c>
+      <c r="G320" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>1144102</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>1140042</v>
+      </c>
+      <c r="F321" t="n">
+        <v>1140122</v>
+      </c>
+      <c r="G321" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>1144103</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.2.step-2</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>1140042</v>
+      </c>
+      <c r="F322" t="n">
+        <v>1140122</v>
+      </c>
+      <c r="G322" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>1144104</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.2.step-3</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>1140042</v>
+      </c>
+      <c r="F323" t="n">
+        <v>1140122</v>
+      </c>
+      <c r="G323" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>1144105</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>1140043</v>
+      </c>
+      <c r="F324" t="n">
+        <v>1140142</v>
+      </c>
+      <c r="G324" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>1144106</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.3.step-2</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>1140043</v>
+      </c>
+      <c r="F325" t="n">
+        <v>1140142</v>
+      </c>
+      <c r="G325" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="n">
+        <v>1144107</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.3.step-3</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>1140043</v>
+      </c>
+      <c r="F326" t="n">
+        <v>1140142</v>
+      </c>
+      <c r="G326" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="n">
+        <v>1144108</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.4.step-1</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>1140044</v>
+      </c>
+      <c r="F327" t="n">
+        <v>1140162</v>
+      </c>
+      <c r="G327" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="n">
+        <v>1144109</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.4.step-2</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>1140044</v>
+      </c>
+      <c r="F328" t="n">
+        <v>1140162</v>
+      </c>
+      <c r="G328" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="n">
+        <v>1144110</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.4.step-3</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>1140044</v>
+      </c>
+      <c r="F329" t="n">
+        <v>1140162</v>
+      </c>
+      <c r="G329" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>1144111</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.5.step-1</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>1140045</v>
+      </c>
+      <c r="F330" t="n">
+        <v>1140182</v>
+      </c>
+      <c r="G330" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>1144112</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.5.step-2</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>1140045</v>
+      </c>
+      <c r="F331" t="n">
+        <v>1140182</v>
+      </c>
+      <c r="G331" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>1144113</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.5.step-3</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>1140045</v>
+      </c>
+      <c r="F332" t="n">
+        <v>1140182</v>
+      </c>
+      <c r="G332" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>1144114</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.6.step-1</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>1140046</v>
+      </c>
+      <c r="F333" t="n">
+        <v>1140202</v>
+      </c>
+      <c r="G333" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>1144115</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.6.step-2</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>1140046</v>
+      </c>
+      <c r="F334" t="n">
+        <v>1140202</v>
+      </c>
+      <c r="G334" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="n">
+        <v>1144116</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.6.step-3</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>1140046</v>
+      </c>
+      <c r="F335" t="n">
+        <v>1140202</v>
+      </c>
+      <c r="G335" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="n">
+        <v>1144117</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.7.step-1</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>1140047</v>
+      </c>
+      <c r="F336" t="n">
+        <v>1140222</v>
+      </c>
+      <c r="G336" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="n">
+        <v>1144118</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.7.step-2</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>1140047</v>
+      </c>
+      <c r="F337" t="n">
+        <v>1140222</v>
+      </c>
+      <c r="G337" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="n">
+        <v>1144119</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.7.step-3</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>1140047</v>
+      </c>
+      <c r="F338" t="n">
+        <v>1140222</v>
+      </c>
+      <c r="G338" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>1144120</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.8.step-1</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>1140048</v>
+      </c>
+      <c r="F339" t="n">
+        <v>1140243</v>
+      </c>
+      <c r="G339" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>1144121</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.8.step-2</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>1140048</v>
+      </c>
+      <c r="F340" t="n">
+        <v>1140243</v>
+      </c>
+      <c r="G340" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>1144122</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.9.step-1</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>1140049</v>
+      </c>
+      <c r="F341" t="n">
+        <v>1140262</v>
+      </c>
+      <c r="G341" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="n">
+        <v>1144123</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.9.step-2</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>1140049</v>
+      </c>
+      <c r="F342" t="n">
+        <v>1140262</v>
+      </c>
+      <c r="G342" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="n">
+        <v>1144124</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.10.step-1</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>1140050</v>
+      </c>
+      <c r="F343" t="n">
+        <v>1140282</v>
+      </c>
+      <c r="G343" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="n">
+        <v>1144125</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.10.step-2</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>1140050</v>
+      </c>
+      <c r="F344" t="n">
+        <v>1140282</v>
+      </c>
+      <c r="G344" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="n">
+        <v>1144126</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.11.step-1</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>1140051</v>
+      </c>
+      <c r="F345" t="n">
+        <v>1140302</v>
+      </c>
+      <c r="G345" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="n">
+        <v>1144127</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.11.step-2</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>1140051</v>
+      </c>
+      <c r="F346" t="n">
+        <v>1140302</v>
+      </c>
+      <c r="G346" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="n">
+        <v>1144128</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.12.step-1</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="F347" t="n">
+        <v>1140325</v>
+      </c>
+      <c r="G347" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="n">
+        <v>1144129</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.12.step-2</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="F348" t="n">
+        <v>1140325</v>
+      </c>
+      <c r="G348" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="n">
+        <v>1144130</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.12.step-3</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="F349" t="n">
+        <v>1140325</v>
+      </c>
+      <c r="G349" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="n">
+        <v>1144131</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.12.step-4</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="F350" t="n">
+        <v>1140325</v>
+      </c>
+      <c r="G350" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="n">
+        <v>1144132</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.12.step-5</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="F351" t="n">
+        <v>1140325</v>
+      </c>
+      <c r="G351" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J351"/>
+  <dimension ref="A1:J358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7175,6 +7175,139 @@
         <v>0</v>
       </c>
     </row>
+    <row r="352">
+      <c r="B352" t="n">
+        <v>1154101</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="F352" t="n">
+        <v>1150105</v>
+      </c>
+      <c r="G352" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="n">
+        <v>1154102</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.1.step-2</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="F353" t="n">
+        <v>1150105</v>
+      </c>
+      <c r="G353" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="n">
+        <v>1154103</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.1.step-3</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="F354" t="n">
+        <v>1150105</v>
+      </c>
+      <c r="G354" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="n">
+        <v>1154104</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.1.step-4</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="F355" t="n">
+        <v>1150105</v>
+      </c>
+      <c r="G355" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="n">
+        <v>1154105</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.1.step-5</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="F356" t="n">
+        <v>1150105</v>
+      </c>
+      <c r="G356" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="n">
+        <v>1154106</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>1150042</v>
+      </c>
+      <c r="F357" t="n">
+        <v>1150122</v>
+      </c>
+      <c r="G357" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="n">
+        <v>1154107</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>1150043</v>
+      </c>
+      <c r="F358" t="n">
+        <v>1150142</v>
+      </c>
+      <c r="G358" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/AiState.xlsx
+++ b/config/data/AiState.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -962,6 +962,6352 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>980701</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>980010</v>
+      </c>
+      <c r="F25" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>980702</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>980010</v>
+      </c>
+      <c r="F26" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>980703</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>980010</v>
+      </c>
+      <c r="F27" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>980704</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-1.state-4</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>980010</v>
+      </c>
+      <c r="F28" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>980705</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-1.state-5</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>980010</v>
+      </c>
+      <c r="F29" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>980706</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>980011</v>
+      </c>
+      <c r="F30" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>980707</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>980011</v>
+      </c>
+      <c r="F31" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>980708</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>980011</v>
+      </c>
+      <c r="F32" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>980709</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-2.state-4</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>980011</v>
+      </c>
+      <c r="F33" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>980710</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-2.state-5</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>980011</v>
+      </c>
+      <c r="F34" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>980711</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-3.state-1</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>980012</v>
+      </c>
+      <c r="F35" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>980712</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-3.state-2</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>980012</v>
+      </c>
+      <c r="F36" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>980713</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-3.state-3</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>980012</v>
+      </c>
+      <c r="F37" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>980714</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-3.state-4</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>980012</v>
+      </c>
+      <c r="F38" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>980715</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.ai.phase-3.state-5</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>980012</v>
+      </c>
+      <c r="F39" t="n">
+        <v>980105</v>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>990701</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>990010</v>
+      </c>
+      <c r="F40" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>990702</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>990010</v>
+      </c>
+      <c r="F41" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>990703</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>990010</v>
+      </c>
+      <c r="F42" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>990704</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>990011</v>
+      </c>
+      <c r="F43" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>990705</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>990011</v>
+      </c>
+      <c r="F44" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>990706</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>990011</v>
+      </c>
+      <c r="F45" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>990707</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-3.state-1</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>990012</v>
+      </c>
+      <c r="F46" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>990708</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-3.state-2</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>990012</v>
+      </c>
+      <c r="F47" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>990709</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.ai.phase-3.state-3</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>990012</v>
+      </c>
+      <c r="F48" t="n">
+        <v>990105</v>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1000701</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1000702</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1000703</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1000704</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-1.state-4</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1000705</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-1.state-5</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1000706</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1000707</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1000708</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1000709</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-2.state-4</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1000710</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.ai.phase-2.state-5</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1000102</v>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1010701</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.ai.initial-bellow</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="G59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1010702</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.ai.initial-absorption</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1010703</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.ai.rain-one</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1010704</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.ai.molten</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1010705</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.ai.rain-two</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1010706</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.ai.reset-absorption</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1010010</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1010101</v>
+      </c>
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1020701</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1020010</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1020702</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1020010</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1020703</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1020010</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1020704</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-1.state-4</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1020010</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1020705</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1020706</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1020707</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1020708</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-2.state-4</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1020709</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-2.state-5</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1020710</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-2.state-6</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1020011</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1020711</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-3.state-1</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1020712</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-3.state-2</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1020713</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-3.state-3</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1020714</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-3.state-4</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1020715</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-3.state-5</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1020716</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.ai.phase-3.state-6</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1020012</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1020101</v>
+      </c>
+      <c r="G80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1030701</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1030010</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1030702</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1030010</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1030703</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1030010</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1030704</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1030705</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1030706</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1030707</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-2.state-4</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1030708</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-2.state-5</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1030709</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-2.state-6</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1030011</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1030710</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-3.state-1</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1030711</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-3.state-2</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1030712</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-3.state-3</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1030713</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-3.state-4</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1030714</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-3.state-5</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1030715</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.ai.phase-3.state-6</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1030012</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1030101</v>
+      </c>
+      <c r="G95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1040701</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1040010</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1040702</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1040010</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1040703</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1040010</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1040704</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-1.state-4</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1040010</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1040705</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1040706</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1040707</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1040708</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-4</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1040709</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-5</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1040710</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-6</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1040711</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-7</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1040712</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-8</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G107" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1040713</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-9</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1040714</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-2.state-10</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1040011</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G109" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1040715</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-1</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1040716</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-2</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1040717</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-3</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1040718</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-4</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1040719</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-5</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1040720</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-6</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1040721</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-7</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1040722</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-8</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1040723</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-9</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1040724</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.ai.phase-3.state-10</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1040012</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1040101</v>
+      </c>
+      <c r="G119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1050701</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.ai.initial-lament</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1050101</v>
+      </c>
+      <c r="G120" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1050702</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.ai.initial-absorption</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1050101</v>
+      </c>
+      <c r="G121" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1050703</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.ai.rain</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1050101</v>
+      </c>
+      <c r="G122" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1050704</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.ai.enhanced-lament</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1050101</v>
+      </c>
+      <c r="G123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1050705</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.ai.reset-absorption</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1050010</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1050101</v>
+      </c>
+      <c r="G124" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1060701</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-1.state-1</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1060010</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1060702</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-1.state-2</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1060010</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G126" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1060703</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-1.state-3</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1060010</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1060704</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-1.state-4</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1060010</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>1060721</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-2.state-1</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1060011</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G129" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>1060722</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-2.state-2</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1060011</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>1060723</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-2.state-3</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1060011</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>1060724</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-2.state-4</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1060011</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1060741</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-3.state-1</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1060012</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1060742</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-3.state-2</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1060012</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>1060743</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-3.state-3</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1060012</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G135" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1060744</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-3.state-4</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1060012</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G136" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>1060745</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.ai.phase-3.state-5</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1060012</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1060101</v>
+      </c>
+      <c r="G137" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>1070701</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-1.step-1-midnight</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1070010</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G138" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>1070702</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-1.step-2-caressing</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1070010</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>1070703</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-1.step-3-mockery</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1070010</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G140" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>1070704</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-1.step-4-spirit</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1070010</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G141" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>1070705</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-2.step-1-midnight</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1070011</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G142" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>1070706</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-2.step-2-caressing</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1070011</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G143" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>1070707</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-2.step-3-mockery</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1070011</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G144" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>1070708</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-2.step-4-psychological</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1070011</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G145" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1070709</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-3.step-1-caressing</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1070012</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G146" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>1070710</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-3.step-2-mockery</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1070012</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G147" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1070711</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-3.step-3-seething</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1070012</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>1070712</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.ai.phase-3.step-4-psychological</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1070012</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1070103</v>
+      </c>
+      <c r="G149" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>1080701</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-1.step-1-emergency</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1080010</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G150" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>1080702</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-1.step-2-banishing</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1080010</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G151" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>1080703</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-1.step-3-burning</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1080010</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G152" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>1080704</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-1.step-4-power</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1080010</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>1080705</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-2.step-1-tactical</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1080011</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G154" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1080706</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-2.step-2-bombardment</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1080011</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G155" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>1080707</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-2.step-3-banishing</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1080011</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G156" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>1080708</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-2.step-4-burning</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1080011</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G157" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>1080709</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-2.step-5-power</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1080011</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>1080710</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-3.step-1-boost</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1080012</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G159" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>1080711</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-3.step-2-bombardment</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1080012</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G160" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>1080712</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-3.step-3-banishing</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1080012</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G161" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>1080713</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.ai.phase-3.step-4-burning</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1080012</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1080101</v>
+      </c>
+      <c r="G162" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1094101</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1090041</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1090102</v>
+      </c>
+      <c r="G163" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>1094102</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1090042</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1090122</v>
+      </c>
+      <c r="G164" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1094103</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.2.step-2</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1090042</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1090122</v>
+      </c>
+      <c r="G165" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>1094104</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.2.step-3</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1090042</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1090122</v>
+      </c>
+      <c r="G166" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>1094105</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.2.step-4</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1090042</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1090122</v>
+      </c>
+      <c r="G167" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>1094106</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1090043</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1090142</v>
+      </c>
+      <c r="G168" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>1094107</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.3.step-2</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1090043</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1090142</v>
+      </c>
+      <c r="G169" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>1094108</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.3.step-3</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1090043</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1090142</v>
+      </c>
+      <c r="G170" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>1094109</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.3.step-4</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1090043</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1090142</v>
+      </c>
+      <c r="G171" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>1094110</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.4.step-1</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1090044</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1090162</v>
+      </c>
+      <c r="G172" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1094111</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.4.step-2</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1090044</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1090162</v>
+      </c>
+      <c r="G173" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>1094112</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.5.step-1</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1090045</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1090182</v>
+      </c>
+      <c r="G174" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>1094113</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.6.step-1</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1090046</v>
+      </c>
+      <c r="F175" t="n">
+        <v>1090202</v>
+      </c>
+      <c r="G175" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>1094114</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.6.step-2</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1090046</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1090202</v>
+      </c>
+      <c r="G176" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>1094115</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.6.step-3</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1090046</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1090202</v>
+      </c>
+      <c r="G177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>1094116</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.7.step-1</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1090222</v>
+      </c>
+      <c r="G178" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>1094117</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.7.step-2</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1090222</v>
+      </c>
+      <c r="G179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>1094118</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.7.step-3</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1090222</v>
+      </c>
+      <c r="G180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>1094119</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.7.step-4</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1090222</v>
+      </c>
+      <c r="G181" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>1094120</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.7.step-5</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1090222</v>
+      </c>
+      <c r="G182" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1094121</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.7.step-6</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1090047</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1090222</v>
+      </c>
+      <c r="G183" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>1094122</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.8.step-1</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1090242</v>
+      </c>
+      <c r="G184" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1094123</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.8.step-2</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1090242</v>
+      </c>
+      <c r="G185" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>1094124</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.8.step-3</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="F186" t="n">
+        <v>1090242</v>
+      </c>
+      <c r="G186" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1094125</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.8.step-4</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1090048</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1090242</v>
+      </c>
+      <c r="G187" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>1094126</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.9.step-1</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1090049</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1090262</v>
+      </c>
+      <c r="G188" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>1094127</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.10.step-1</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1090050</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1090282</v>
+      </c>
+      <c r="G189" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>1094128</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.10.step-2</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1090050</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1090282</v>
+      </c>
+      <c r="G190" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1094129</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.10.step-3</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1090050</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1090282</v>
+      </c>
+      <c r="G191" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>1094130</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.10.step-4</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1090050</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1090282</v>
+      </c>
+      <c r="G192" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>1094131</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.11.step-1</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1090302</v>
+      </c>
+      <c r="G193" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>1094132</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.11.step-2</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1090302</v>
+      </c>
+      <c r="G194" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1094133</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.11.step-3</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1090302</v>
+      </c>
+      <c r="G195" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>1094134</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.11.step-4</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1090302</v>
+      </c>
+      <c r="G196" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>1094135</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.11.step-5</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1090051</v>
+      </c>
+      <c r="F197" t="n">
+        <v>1090302</v>
+      </c>
+      <c r="G197" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1094136</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.12.step-1</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1090052</v>
+      </c>
+      <c r="F198" t="n">
+        <v>1090322</v>
+      </c>
+      <c r="G198" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>1094137</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.ai.12.step-2</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1090052</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1090322</v>
+      </c>
+      <c r="G199" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>1104101</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1100041</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1100102</v>
+      </c>
+      <c r="G200" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>1104102</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.1.step-2</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1100041</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1100102</v>
+      </c>
+      <c r="G201" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1104103</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.1.step-3</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1100041</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1100102</v>
+      </c>
+      <c r="G202" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>1104104</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1100042</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1100122</v>
+      </c>
+      <c r="G203" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>1104105</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>1100043</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1100142</v>
+      </c>
+      <c r="G204" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1104106</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.3.step-2</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>1100043</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1100142</v>
+      </c>
+      <c r="G205" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1104107</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.4.step-1</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1100044</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1100162</v>
+      </c>
+      <c r="G206" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>1104108</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.4.step-2</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>1100044</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1100162</v>
+      </c>
+      <c r="G207" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>1104109</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.4.step-3</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1100044</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1100162</v>
+      </c>
+      <c r="G208" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>1104110</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.4.step-4</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>1100044</v>
+      </c>
+      <c r="F209" t="n">
+        <v>1100162</v>
+      </c>
+      <c r="G209" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>1104111</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.5.step-1</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1100045</v>
+      </c>
+      <c r="F210" t="n">
+        <v>1100182</v>
+      </c>
+      <c r="G210" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>1104112</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.6.step-1</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1100046</v>
+      </c>
+      <c r="F211" t="n">
+        <v>1100202</v>
+      </c>
+      <c r="G211" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>1104113</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.6.step-2</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1100046</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1100202</v>
+      </c>
+      <c r="G212" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>1104114</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.7.step-1</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1100047</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1100224</v>
+      </c>
+      <c r="G213" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>1104115</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.7.step-2</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1100047</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1100224</v>
+      </c>
+      <c r="G214" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>1104116</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.7.step-3</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1100047</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1100224</v>
+      </c>
+      <c r="G215" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>1104117</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.7.step-4</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1100047</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1100224</v>
+      </c>
+      <c r="G216" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>1104118</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.8.step-1</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1100048</v>
+      </c>
+      <c r="F217" t="n">
+        <v>1100244</v>
+      </c>
+      <c r="G217" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>1104119</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.8.step-2</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1100048</v>
+      </c>
+      <c r="F218" t="n">
+        <v>1100244</v>
+      </c>
+      <c r="G218" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>1104120</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.8.step-3</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1100048</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1100244</v>
+      </c>
+      <c r="G219" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>1104121</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.8.step-4</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1100048</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1100244</v>
+      </c>
+      <c r="G220" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>1104122</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.9.step-1</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1100262</v>
+      </c>
+      <c r="G221" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>1104123</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.9.step-2</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1100262</v>
+      </c>
+      <c r="G222" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>1104124</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.9.step-3</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="F223" t="n">
+        <v>1100262</v>
+      </c>
+      <c r="G223" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>1104125</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.9.step-4</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="F224" t="n">
+        <v>1100262</v>
+      </c>
+      <c r="G224" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>1104126</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.9.step-5</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>1100049</v>
+      </c>
+      <c r="F225" t="n">
+        <v>1100262</v>
+      </c>
+      <c r="G225" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>1104127</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.10.step-1</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="F226" t="n">
+        <v>1100282</v>
+      </c>
+      <c r="G226" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>1104128</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.10.step-2</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1100282</v>
+      </c>
+      <c r="G227" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>1104129</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.10.step-3</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="F228" t="n">
+        <v>1100282</v>
+      </c>
+      <c r="G228" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>1104130</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.10.step-4</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="F229" t="n">
+        <v>1100282</v>
+      </c>
+      <c r="G229" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>1104131</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.10.step-5</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>1100050</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1100282</v>
+      </c>
+      <c r="G230" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>1104132</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.11.step-1</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>1100051</v>
+      </c>
+      <c r="F231" t="n">
+        <v>1100302</v>
+      </c>
+      <c r="G231" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>1104133</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.12.step-1</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>1100052</v>
+      </c>
+      <c r="F232" t="n">
+        <v>1100322</v>
+      </c>
+      <c r="G232" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>1104134</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.ai.12.step-2</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1100052</v>
+      </c>
+      <c r="F233" t="n">
+        <v>1100322</v>
+      </c>
+      <c r="G233" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>1114101</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>1110041</v>
+      </c>
+      <c r="F234" t="n">
+        <v>1110102</v>
+      </c>
+      <c r="G234" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>1114102</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.1.step-2</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>1110041</v>
+      </c>
+      <c r="F235" t="n">
+        <v>1110102</v>
+      </c>
+      <c r="G235" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>1114103</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.1.step-3</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>1110041</v>
+      </c>
+      <c r="F236" t="n">
+        <v>1110102</v>
+      </c>
+      <c r="G236" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>1114104</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>1110042</v>
+      </c>
+      <c r="F237" t="n">
+        <v>1110122</v>
+      </c>
+      <c r="G237" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>1114105</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>1110043</v>
+      </c>
+      <c r="F238" t="n">
+        <v>1110142</v>
+      </c>
+      <c r="G238" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>1114106</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.3.step-2</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>1110043</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1110142</v>
+      </c>
+      <c r="G239" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>1114107</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.3.step-3</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1110043</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1110142</v>
+      </c>
+      <c r="G240" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>1114108</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.3.step-4</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>1110043</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1110142</v>
+      </c>
+      <c r="G241" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>1114109</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.4.step-1</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>1110044</v>
+      </c>
+      <c r="F242" t="n">
+        <v>1110162</v>
+      </c>
+      <c r="G242" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>1114110</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.4.step-2</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>1110044</v>
+      </c>
+      <c r="F243" t="n">
+        <v>1110162</v>
+      </c>
+      <c r="G243" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>1114111</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.4.step-3</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1110044</v>
+      </c>
+      <c r="F244" t="n">
+        <v>1110162</v>
+      </c>
+      <c r="G244" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>1114112</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.4.step-4</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>1110044</v>
+      </c>
+      <c r="F245" t="n">
+        <v>1110162</v>
+      </c>
+      <c r="G245" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>1114113</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.5.step-1</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>1110045</v>
+      </c>
+      <c r="F246" t="n">
+        <v>1110182</v>
+      </c>
+      <c r="G246" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>1114114</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.5.step-2</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>1110045</v>
+      </c>
+      <c r="F247" t="n">
+        <v>1110182</v>
+      </c>
+      <c r="G247" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>1114115</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.5.step-3</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>1110045</v>
+      </c>
+      <c r="F248" t="n">
+        <v>1110182</v>
+      </c>
+      <c r="G248" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>1114116</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.6.step-1</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>1110046</v>
+      </c>
+      <c r="F249" t="n">
+        <v>1110202</v>
+      </c>
+      <c r="G249" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>1114117</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.7.step-1</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>1110047</v>
+      </c>
+      <c r="F250" t="n">
+        <v>1110222</v>
+      </c>
+      <c r="G250" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>1114118</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.8.step-1</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>1110048</v>
+      </c>
+      <c r="F251" t="n">
+        <v>1110242</v>
+      </c>
+      <c r="G251" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>1114119</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.9.step-1</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>1110049</v>
+      </c>
+      <c r="F252" t="n">
+        <v>1110262</v>
+      </c>
+      <c r="G252" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>1114120</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.10.step-1</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>1110050</v>
+      </c>
+      <c r="F253" t="n">
+        <v>1110282</v>
+      </c>
+      <c r="G253" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>1114121</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.11.step-1</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="F254" t="n">
+        <v>1110303</v>
+      </c>
+      <c r="G254" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>1114122</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.11.step-2</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="F255" t="n">
+        <v>1110303</v>
+      </c>
+      <c r="G255" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>1114123</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.11.step-3</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="F256" t="n">
+        <v>1110303</v>
+      </c>
+      <c r="G256" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>1114124</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.11.step-4</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="F257" t="n">
+        <v>1110303</v>
+      </c>
+      <c r="G257" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>1114125</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.11.step-5</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>1110051</v>
+      </c>
+      <c r="F258" t="n">
+        <v>1110303</v>
+      </c>
+      <c r="G258" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>1114126</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.ai.12.step-1</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>1110052</v>
+      </c>
+      <c r="F259" t="n">
+        <v>1110322</v>
+      </c>
+      <c r="G259" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>1124101</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>1120041</v>
+      </c>
+      <c r="F260" t="n">
+        <v>1120102</v>
+      </c>
+      <c r="G260" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>1124102</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>1120042</v>
+      </c>
+      <c r="F261" t="n">
+        <v>1120122</v>
+      </c>
+      <c r="G261" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>1124103</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F262" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G262" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>1124104</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-2</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F263" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G263" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>1124105</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-3</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F264" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G264" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>1124106</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-4</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F265" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G265" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>1124107</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-5</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F266" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G266" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>1124108</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-6</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F267" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G267" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>1124109</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.3.step-7</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>1120043</v>
+      </c>
+      <c r="F268" t="n">
+        <v>1120142</v>
+      </c>
+      <c r="G268" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>1124110</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.4.step-1</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>1120044</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1120164</v>
+      </c>
+      <c r="G269" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>1124111</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.4.step-2</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>1120044</v>
+      </c>
+      <c r="F270" t="n">
+        <v>1120164</v>
+      </c>
+      <c r="G270" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>1124112</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.4.step-3</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>1120044</v>
+      </c>
+      <c r="F271" t="n">
+        <v>1120164</v>
+      </c>
+      <c r="G271" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>1124113</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.5.step-1</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>1120045</v>
+      </c>
+      <c r="F272" t="n">
+        <v>1120182</v>
+      </c>
+      <c r="G272" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>1124114</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.6.step-1</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>1120046</v>
+      </c>
+      <c r="F273" t="n">
+        <v>1120202</v>
+      </c>
+      <c r="G273" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>1124115</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.6.step-2</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>1120046</v>
+      </c>
+      <c r="F274" t="n">
+        <v>1120202</v>
+      </c>
+      <c r="G274" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>1124116</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.7.step-1</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>1120047</v>
+      </c>
+      <c r="F275" t="n">
+        <v>1120222</v>
+      </c>
+      <c r="G275" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>1124117</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.7.step-2</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>1120047</v>
+      </c>
+      <c r="F276" t="n">
+        <v>1120222</v>
+      </c>
+      <c r="G276" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>1124118</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.8.step-1</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>1120048</v>
+      </c>
+      <c r="F277" t="n">
+        <v>1120242</v>
+      </c>
+      <c r="G277" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>1124119</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.9.step-1</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>1120049</v>
+      </c>
+      <c r="F278" t="n">
+        <v>1120263</v>
+      </c>
+      <c r="G278" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>1124120</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.10.step-1</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>1120050</v>
+      </c>
+      <c r="F279" t="n">
+        <v>1120283</v>
+      </c>
+      <c r="G279" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>1124121</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.10.step-2</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>1120050</v>
+      </c>
+      <c r="F280" t="n">
+        <v>1120283</v>
+      </c>
+      <c r="G280" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>1124122</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.11.step-1</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>1120051</v>
+      </c>
+      <c r="F281" t="n">
+        <v>1120302</v>
+      </c>
+      <c r="G281" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>1124123</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.ai.12.step-1</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>1120052</v>
+      </c>
+      <c r="F282" t="n">
+        <v>1120322</v>
+      </c>
+      <c r="G282" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>1134101</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>1130041</v>
+      </c>
+      <c r="F283" t="n">
+        <v>1130102</v>
+      </c>
+      <c r="G283" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>1134102</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.1.step-2</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>1130041</v>
+      </c>
+      <c r="F284" t="n">
+        <v>1130102</v>
+      </c>
+      <c r="G284" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>1134103</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.1.step-3</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>1130041</v>
+      </c>
+      <c r="F285" t="n">
+        <v>1130102</v>
+      </c>
+      <c r="G285" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>1134104</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.1.step-4</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>1130041</v>
+      </c>
+      <c r="F286" t="n">
+        <v>1130102</v>
+      </c>
+      <c r="G286" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>1134105</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>1130042</v>
+      </c>
+      <c r="F287" t="n">
+        <v>1130122</v>
+      </c>
+      <c r="G287" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>1134106</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>1130043</v>
+      </c>
+      <c r="F288" t="n">
+        <v>1130145</v>
+      </c>
+      <c r="G288" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>1134107</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.3.step-2</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>1130043</v>
+      </c>
+      <c r="F289" t="n">
+        <v>1130145</v>
+      </c>
+      <c r="G289" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>1134108</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.3.step-3</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>1130043</v>
+      </c>
+      <c r="F290" t="n">
+        <v>1130145</v>
+      </c>
+      <c r="G290" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>1134109</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.3.step-4</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>1130043</v>
+      </c>
+      <c r="F291" t="n">
+        <v>1130145</v>
+      </c>
+      <c r="G291" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>1134110</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.4.step-1</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>1130044</v>
+      </c>
+      <c r="F292" t="n">
+        <v>1130167</v>
+      </c>
+      <c r="G292" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>1134111</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.4.step-2</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>1130044</v>
+      </c>
+      <c r="F293" t="n">
+        <v>1130167</v>
+      </c>
+      <c r="G293" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>1134112</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.4.step-3</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>1130044</v>
+      </c>
+      <c r="F294" t="n">
+        <v>1130167</v>
+      </c>
+      <c r="G294" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>1134113</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.4.step-4</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>1130044</v>
+      </c>
+      <c r="F295" t="n">
+        <v>1130167</v>
+      </c>
+      <c r="G295" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>1134114</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.5.step-1</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>1130045</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1130187</v>
+      </c>
+      <c r="G296" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>1134115</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.5.step-2</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>1130045</v>
+      </c>
+      <c r="F297" t="n">
+        <v>1130187</v>
+      </c>
+      <c r="G297" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>1134116</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.5.step-3</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>1130045</v>
+      </c>
+      <c r="F298" t="n">
+        <v>1130187</v>
+      </c>
+      <c r="G298" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>1134117</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.5.step-4</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>1130045</v>
+      </c>
+      <c r="F299" t="n">
+        <v>1130187</v>
+      </c>
+      <c r="G299" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>1134118</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.6.step-1</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>1130046</v>
+      </c>
+      <c r="F300" t="n">
+        <v>1130203</v>
+      </c>
+      <c r="G300" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>1134119</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.6.step-2</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>1130046</v>
+      </c>
+      <c r="F301" t="n">
+        <v>1130203</v>
+      </c>
+      <c r="G301" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>1134120</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.7.step-1</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>1130047</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1130222</v>
+      </c>
+      <c r="G302" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>1134121</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.8.step-1</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>1130048</v>
+      </c>
+      <c r="F303" t="n">
+        <v>1130245</v>
+      </c>
+      <c r="G303" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>1134122</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.8.step-2</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>1130048</v>
+      </c>
+      <c r="F304" t="n">
+        <v>1130245</v>
+      </c>
+      <c r="G304" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>1134123</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.8.step-3</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>1130048</v>
+      </c>
+      <c r="F305" t="n">
+        <v>1130245</v>
+      </c>
+      <c r="G305" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>1134124</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.8.step-4</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>1130048</v>
+      </c>
+      <c r="F306" t="n">
+        <v>1130245</v>
+      </c>
+      <c r="G306" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>1134125</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.9.step-1</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>1130049</v>
+      </c>
+      <c r="F307" t="n">
+        <v>1130262</v>
+      </c>
+      <c r="G307" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>1134126</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.10.step-1</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>1130050</v>
+      </c>
+      <c r="F308" t="n">
+        <v>1130284</v>
+      </c>
+      <c r="G308" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>1134127</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.10.step-2</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>1130050</v>
+      </c>
+      <c r="F309" t="n">
+        <v>1130284</v>
+      </c>
+      <c r="G309" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>1134128</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.10.step-3</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>1130050</v>
+      </c>
+      <c r="F310" t="n">
+        <v>1130284</v>
+      </c>
+      <c r="G310" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>1134129</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.10.step-4</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>1130050</v>
+      </c>
+      <c r="F311" t="n">
+        <v>1130284</v>
+      </c>
+      <c r="G311" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>1134130</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.11.step-1</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>1130051</v>
+      </c>
+      <c r="F312" t="n">
+        <v>1130304</v>
+      </c>
+      <c r="G312" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>1134131</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.11.step-2</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>1130051</v>
+      </c>
+      <c r="F313" t="n">
+        <v>1130304</v>
+      </c>
+      <c r="G313" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>1134132</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.11.step-3</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>1130051</v>
+      </c>
+      <c r="F314" t="n">
+        <v>1130304</v>
+      </c>
+      <c r="G314" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>1134133</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.11.step-4</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>1130051</v>
+      </c>
+      <c r="F315" t="n">
+        <v>1130304</v>
+      </c>
+      <c r="G315" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>1134134</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.12.step-1</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>1130052</v>
+      </c>
+      <c r="F316" t="n">
+        <v>1130325</v>
+      </c>
+      <c r="G316" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="n">
+        <v>1134135</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.12.step-2</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>1130052</v>
+      </c>
+      <c r="F317" t="n">
+        <v>1130325</v>
+      </c>
+      <c r="G317" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="n">
+        <v>1134136</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.12.step-3</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>1130052</v>
+      </c>
+      <c r="F318" t="n">
+        <v>1130325</v>
+      </c>
+      <c r="G318" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="n">
+        <v>1134137</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.ai.12.step-4</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>1130052</v>
+      </c>
+      <c r="F319" t="n">
+        <v>1130325</v>
+      </c>
+      <c r="G319" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="n">
+        <v>1144101</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>1140041</v>
+      </c>
+      <c r="F320" t="n">
+        <v>1140102</v>
+      </c>
+      <c r="G320" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>1144102</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>1140042</v>
+      </c>
+      <c r="F321" t="n">
+        <v>1140122</v>
+      </c>
+      <c r="G321" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>1144103</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.2.step-2</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>1140042</v>
+      </c>
+      <c r="F322" t="n">
+        <v>1140122</v>
+      </c>
+      <c r="G322" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>1144104</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.2.step-3</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>1140042</v>
+      </c>
+      <c r="F323" t="n">
+        <v>1140122</v>
+      </c>
+      <c r="G323" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>1144105</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>1140043</v>
+      </c>
+      <c r="F324" t="n">
+        <v>1140142</v>
+      </c>
+      <c r="G324" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>1144106</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.3.step-2</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>1140043</v>
+      </c>
+      <c r="F325" t="n">
+        <v>1140142</v>
+      </c>
+      <c r="G325" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="n">
+        <v>1144107</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.3.step-3</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>1140043</v>
+      </c>
+      <c r="F326" t="n">
+        <v>1140142</v>
+      </c>
+      <c r="G326" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="n">
+        <v>1144108</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.4.step-1</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>1140044</v>
+      </c>
+      <c r="F327" t="n">
+        <v>1140162</v>
+      </c>
+      <c r="G327" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="n">
+        <v>1144109</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.4.step-2</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>1140044</v>
+      </c>
+      <c r="F328" t="n">
+        <v>1140162</v>
+      </c>
+      <c r="G328" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="n">
+        <v>1144110</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.4.step-3</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>1140044</v>
+      </c>
+      <c r="F329" t="n">
+        <v>1140162</v>
+      </c>
+      <c r="G329" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>1144111</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.5.step-1</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>1140045</v>
+      </c>
+      <c r="F330" t="n">
+        <v>1140182</v>
+      </c>
+      <c r="G330" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>1144112</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.5.step-2</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>1140045</v>
+      </c>
+      <c r="F331" t="n">
+        <v>1140182</v>
+      </c>
+      <c r="G331" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>1144113</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.5.step-3</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>1140045</v>
+      </c>
+      <c r="F332" t="n">
+        <v>1140182</v>
+      </c>
+      <c r="G332" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>1144114</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.6.step-1</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>1140046</v>
+      </c>
+      <c r="F333" t="n">
+        <v>1140202</v>
+      </c>
+      <c r="G333" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>1144115</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.6.step-2</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>1140046</v>
+      </c>
+      <c r="F334" t="n">
+        <v>1140202</v>
+      </c>
+      <c r="G334" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="n">
+        <v>1144116</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.6.step-3</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>1140046</v>
+      </c>
+      <c r="F335" t="n">
+        <v>1140202</v>
+      </c>
+      <c r="G335" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="n">
+        <v>1144117</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.7.step-1</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>1140047</v>
+      </c>
+      <c r="F336" t="n">
+        <v>1140222</v>
+      </c>
+      <c r="G336" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="n">
+        <v>1144118</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.7.step-2</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>1140047</v>
+      </c>
+      <c r="F337" t="n">
+        <v>1140222</v>
+      </c>
+      <c r="G337" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="n">
+        <v>1144119</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.7.step-3</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>1140047</v>
+      </c>
+      <c r="F338" t="n">
+        <v>1140222</v>
+      </c>
+      <c r="G338" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>1144120</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.8.step-1</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>1140048</v>
+      </c>
+      <c r="F339" t="n">
+        <v>1140243</v>
+      </c>
+      <c r="G339" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>1144121</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.8.step-2</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>1140048</v>
+      </c>
+      <c r="F340" t="n">
+        <v>1140243</v>
+      </c>
+      <c r="G340" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>1144122</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.9.step-1</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>1140049</v>
+      </c>
+      <c r="F341" t="n">
+        <v>1140262</v>
+      </c>
+      <c r="G341" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="n">
+        <v>1144123</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.9.step-2</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>1140049</v>
+      </c>
+      <c r="F342" t="n">
+        <v>1140262</v>
+      </c>
+      <c r="G342" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="n">
+        <v>1144124</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.10.step-1</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>1140050</v>
+      </c>
+      <c r="F343" t="n">
+        <v>1140282</v>
+      </c>
+      <c r="G343" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="n">
+        <v>1144125</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.10.step-2</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>1140050</v>
+      </c>
+      <c r="F344" t="n">
+        <v>1140282</v>
+      </c>
+      <c r="G344" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="n">
+        <v>1144126</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.11.step-1</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>1140051</v>
+      </c>
+      <c r="F345" t="n">
+        <v>1140302</v>
+      </c>
+      <c r="G345" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="n">
+        <v>1144127</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.11.step-2</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>1140051</v>
+      </c>
+      <c r="F346" t="n">
+        <v>1140302</v>
+      </c>
+      <c r="G346" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="n">
+        <v>1144128</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.12.step-1</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="F347" t="n">
+        <v>1140325</v>
+      </c>
+      <c r="G347" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="n">
+        <v>1144129</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.12.step-2</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="F348" t="n">
+        <v>1140325</v>
+      </c>
+      <c r="G348" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="n">
+        <v>1144130</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.12.step-3</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="F349" t="n">
+        <v>1140325</v>
+      </c>
+      <c r="G349" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="n">
+        <v>1144131</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.12.step-4</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="F350" t="n">
+        <v>1140325</v>
+      </c>
+      <c r="G350" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="n">
+        <v>1144132</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.ai.12.step-5</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>1140052</v>
+      </c>
+      <c r="F351" t="n">
+        <v>1140325</v>
+      </c>
+      <c r="G351" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="n">
+        <v>1154101</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.1.step-1</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="F352" t="n">
+        <v>1150105</v>
+      </c>
+      <c r="G352" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="n">
+        <v>1154102</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.1.step-2</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="F353" t="n">
+        <v>1150105</v>
+      </c>
+      <c r="G353" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="n">
+        <v>1154103</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.1.step-3</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="F354" t="n">
+        <v>1150105</v>
+      </c>
+      <c r="G354" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="n">
+        <v>1154104</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.1.step-4</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="F355" t="n">
+        <v>1150105</v>
+      </c>
+      <c r="G355" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="n">
+        <v>1154105</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.1.step-5</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>1150041</v>
+      </c>
+      <c r="F356" t="n">
+        <v>1150105</v>
+      </c>
+      <c r="G356" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="n">
+        <v>1154106</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.2.step-1</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>1150042</v>
+      </c>
+      <c r="F357" t="n">
+        <v>1150122</v>
+      </c>
+      <c r="G357" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="n">
+        <v>1154107</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s18.ai.3.step-1</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>1150043</v>
+      </c>
+      <c r="F358" t="n">
+        <v>1150142</v>
+      </c>
+      <c r="G358" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
